--- a/01a/assignment_01/experiment4.xlsx
+++ b/01a/assignment_01/experiment4.xlsx
@@ -399,7 +399,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,13 +409,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -476,10 +470,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -797,7 +791,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="561.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="511.14785714285716" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -812,7 +806,7 @@
     <col min="14" max="14" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,7 +873,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="6">
-        <v>0.00006254999999999999</v>
+        <v>0.00006255</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="5">
